--- a/bom/BOM.xlsx
+++ b/bom/BOM.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">오리지널!$A$5:$P$36</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'일반 서보 버전'!$A$5:$P$26</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'저렴한 버전'!$A$5:$P$25</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'저렴한 버전'!$A$5:$P$26</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -143,7 +143,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="442">
   <si>
     <r>
       <rPr>
@@ -4196,56 +4196,247 @@
     <t xml:space="preserve">저렴한 버전은 탭볼트 직결</t>
   </si>
   <si>
-    <t xml:space="preserve">보강판</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1 mm </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">카본 판 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">100×100</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.aliexpress.com/w/wholesale-carbon-fiber-plate-1mm-100x100.html?SortType=price_asc</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">upper_leg_rigidity_plate ×2. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">저렴한 버전은 출력으로 두께 보강</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">판재 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">종 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">알루미늄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">레이저 가공</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 1 mm ×5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보강판</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">몸통판</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">롤판</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2) + 2 mm ×2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목판</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 가공 업체</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://search.shopping.naver.com/search/all?query=%EC%95%8C%EB%A3%A8%EB%AF%B8%EB%8A%84+%EB%A0%88%EC%9D%B4%EC%A0%80+%EA%B0%80%EA%B3%B5+%EC%86%8C%EB%9F%89&amp;sort=price_asc</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JLCCNC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">판금</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: https://jlccnc.com/ / PCBWay: https://www.pcbway.com/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DXF: cad/plates/dynamixel. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">소량 최소주문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배송비 때문에 견적 편차 큼 — 견적 받아 수정</t>
     </r>
   </si>
   <si>
@@ -4904,6 +5095,199 @@
   <si>
     <r>
       <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">판재 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">종 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(FR4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PCB </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">업체 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FR4 1.0 mm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">외곽 가공 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보강판</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">몸통판</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">롤판</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목판은 출력</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HAT PCB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">와 같이 주문하면 배송비 합산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">알루미늄보다 강성 낮지만 출력물보다 훨씬 단단</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <b val="true"/>
         <sz val="14"/>
         <rFont val="Arial"/>
@@ -6708,6 +7092,9 @@
     <t xml:space="preserve">bearing_roll</t>
   </si>
   <si>
+    <t xml:space="preserve">판재</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -6715,7 +7102,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">판재</t>
+      <t xml:space="preserve">알루미늄 </t>
     </r>
     <r>
       <rPr>
@@ -6725,8 +7112,10 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
+      <t xml:space="preserve">1 mm</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -6734,10 +7123,217 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">고관절 롤 베어링판 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보스 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 생략</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) — DXF: cad/plates/dynamixel</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/bearing_roll.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bottom_head_shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/bottom_head_shell.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">elec_rpi_robot_hat_pcb</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자작 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PCB</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">65×30 HAT</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">반이중 버스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">오디오 등 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">직접 설계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/elec_rpi_robot_hat_pcb.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">face_part</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/face_part.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foot_left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/foot_left.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foot_right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/foot_right.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hip_l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/hip_l.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jaw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/jaw.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jaw_soft</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">출력</t>
     </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -6746,7 +7342,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3 mm </t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -6755,7 +7351,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">판 </t>
+      <t xml:space="preserve">연질</t>
     </r>
     <r>
       <rPr>
@@ -6765,6 +7361,478 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TPU 95A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부리 아래 연질부</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/jaw_soft.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">left_shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/left_shell.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/leg.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">구매품</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">광각 렌즈</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IMX219 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">카메라용</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/lens.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m12_lens_holder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/m12_lens_holder.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">motor_support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/motor_support.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">neck</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">알루미늄 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2 mm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목 연결판 — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DXF: cad/plates/dynamixel</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/neck.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">neck_pitch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/neck_pitch.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">noenoeil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/noenoeil.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">np_f970</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Sony NP-F </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">계열 배터리 외형</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모델은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NP-F970 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">크기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실물은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NP-F550</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/np_f970.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pcb__raspberry_pi_zero_2_w</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Radxa Zero 3W (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">동일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">65×30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">폼팩터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모델은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Pi Zero 2W </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자리표시자</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/pcb__raspberry_pi_zero_2_w.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">power_support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/power_support.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">right_shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/right_shell.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">롤러 옵션</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/rim.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">roller_blade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/roller_blade.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seeed_bearing__configuration__22x16x4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">볼베어링 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16×22×4</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/seeed_bearing__configuration__22x16x4.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seeed_bearing__configuration_default</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">볼베어링 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10×15×3</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">소형 베어링</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/seeed_bearing__configuration_default.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soft_mouth_top</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부리 위 연질부</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/soft_mouth_top.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sole_left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/sole_left.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sole_right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/sole_right.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">speaker</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">35×25×7 mm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">소형 스피커</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/speaker.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tire</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">롤러 타이어 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">(</t>
     </r>
     <r>
@@ -6774,7 +7842,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">추정</t>
+      <t xml:space="preserve">선택</t>
     </r>
     <r>
       <rPr>
@@ -6784,25 +7852,8 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">고관절 롤 베어링 판</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/bearing_roll.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bottom_head_shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/bottom_head_shell.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">elec_rpi_robot_hat_pcb</t>
-  </si>
-  <si>
+      <t xml:space="preserve">) </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -6810,798 +7861,136 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">자작 </t>
-    </r>
+      <t xml:space="preserve">롤러 옵션</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/tire.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">top_head_shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/top_head_shell.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trunk_base</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PCB</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">65×30 HAT</t>
-  </si>
-  <si>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">몸통 바닥판 </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">반이중 버스</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(+</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">높이 </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전원</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2 mm </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보스 </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">오디오 등 </t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개는 생략</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">직접 설계</t>
-    </r>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) — DXF: cad/plates/dynamixel</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/trunk_base.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upper_leg_left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/upper_leg_left.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upper_leg_right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets/upper_leg_right.stl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upper_leg_rigidity_plate</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/elec_rpi_robot_hat_pcb.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">face_part</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/face_part.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foot_left</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/foot_left.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foot_right</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/foot_right.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hip_l</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/hip_l.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jaw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/jaw.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jaw_soft</t>
-  </si>
-  <si>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">허벅지 보강판 — </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">출력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연질</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">TPU 95A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">부리 아래 연질부</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/jaw_soft.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">left_shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/left_shell.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">leg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/leg.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">구매품</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">M12 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">광각 렌즈</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IMX219 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">카메라용</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/lens.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m12_lens_holder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/m12_lens_holder.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">motor_support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/motor_support.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">neck</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2 mm </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">판 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">추정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/neck.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">neck_pitch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/neck_pitch.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">noenoeil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/noenoeil.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">np_f970</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Sony NP-F </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">계열 배터리 외형</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">모델은 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NP-F970 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">크기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">실물은 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NP-F550</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/np_f970.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pcb__raspberry_pi_zero_2_w</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Radxa Zero 3W (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">동일 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">65×30 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">폼팩터</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">모델은 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Pi Zero 2W </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">자리표시자</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/pcb__raspberry_pi_zero_2_w.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">power_support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/power_support.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">right_shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/right_shell.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">롤러 옵션</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/rim.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">roller_blade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/roller_blade.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">seeed_bearing__configuration__22x16x4</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">볼베어링 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16×22×4</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/seeed_bearing__configuration__22x16x4.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">seeed_bearing__configuration_default</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">볼베어링 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10×15×3</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">소형 베어링</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/seeed_bearing__configuration_default.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soft_mouth_top</t>
-  </si>
-  <si>
-    <t xml:space="preserve">부리 위 연질부</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/soft_mouth_top.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sole_left</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/sole_left.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sole_right</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/sole_right.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">speaker</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">35×25×7 mm </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">소형 스피커</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/speaker.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tire</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">롤러 타이어 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">선택</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">롤러 옵션</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/tire.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">top_head_shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/top_head_shell.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trunk_base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">몸통 바닥판</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/trunk_base.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upper_leg_left</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/upper_leg_left.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upper_leg_right</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets/upper_leg_right.stl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upper_leg_rigidity_plate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">판재</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1 mm CF/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">알루미늄 판 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">추정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">두께 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1 mm — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">출력이면 보강 필요</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DXF: cad/plates/dynamixel</t>
     </r>
   </si>
   <si>
@@ -8461,7 +8850,7 @@
         <v>498630</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">SUMIFS('저렴한 버전'!$J$6:$J$25,'저렴한 버전'!$A$6:$A$25,A8)</f>
+        <f aca="false">SUMIFS('저렴한 버전'!$J$6:$J$26,'저렴한 버전'!$A$6:$A$26,A8)</f>
         <v>372100</v>
       </c>
       <c r="D8" s="6" t="n">
@@ -8478,7 +8867,7 @@
         <v>31000</v>
       </c>
       <c r="C9" s="6" t="n">
-        <f aca="false">SUMIFS('저렴한 버전'!$J$6:$J$25,'저렴한 버전'!$A$6:$A$25,A9)</f>
+        <f aca="false">SUMIFS('저렴한 버전'!$J$6:$J$26,'저렴한 버전'!$A$6:$A$26,A9)</f>
         <v>37000</v>
       </c>
       <c r="D9" s="6" t="n">
@@ -8495,7 +8884,7 @@
         <v>126642</v>
       </c>
       <c r="C10" s="6" t="n">
-        <f aca="false">SUMIFS('저렴한 버전'!$J$6:$J$25,'저렴한 버전'!$A$6:$A$25,A10)</f>
+        <f aca="false">SUMIFS('저렴한 버전'!$J$6:$J$26,'저렴한 버전'!$A$6:$A$26,A10)</f>
         <v>37356</v>
       </c>
       <c r="D10" s="6" t="n">
@@ -8512,7 +8901,7 @@
         <v>7000</v>
       </c>
       <c r="C11" s="6" t="n">
-        <f aca="false">SUMIFS('저렴한 버전'!$J$6:$J$25,'저렴한 버전'!$A$6:$A$25,A11)</f>
+        <f aca="false">SUMIFS('저렴한 버전'!$J$6:$J$26,'저렴한 버전'!$A$6:$A$26,A11)</f>
         <v>0</v>
       </c>
       <c r="D11" s="6" t="n">
@@ -8529,7 +8918,7 @@
         <v>60500</v>
       </c>
       <c r="C12" s="6" t="n">
-        <f aca="false">SUMIFS('저렴한 버전'!$J$6:$J$25,'저렴한 버전'!$A$6:$A$25,A12)</f>
+        <f aca="false">SUMIFS('저렴한 버전'!$J$6:$J$26,'저렴한 버전'!$A$6:$A$26,A12)</f>
         <v>33000</v>
       </c>
       <c r="D12" s="6" t="n">
@@ -8546,7 +8935,7 @@
         <v>15230</v>
       </c>
       <c r="C13" s="6" t="n">
-        <f aca="false">SUMIFS('저렴한 버전'!$J$6:$J$25,'저렴한 버전'!$A$6:$A$25,A13)</f>
+        <f aca="false">SUMIFS('저렴한 버전'!$J$6:$J$26,'저렴한 버전'!$A$6:$A$26,A13)</f>
         <v>14810</v>
       </c>
       <c r="D13" s="6" t="n">
@@ -8560,11 +8949,11 @@
       </c>
       <c r="B14" s="6" t="n">
         <f aca="false">SUMIFS(오리지널!$J$6:$J$36,오리지널!$A$6:$A$36,A14)</f>
-        <v>35600</v>
+        <v>69600</v>
       </c>
       <c r="C14" s="6" t="n">
-        <f aca="false">SUMIFS('저렴한 버전'!$J$6:$J$25,'저렴한 버전'!$A$6:$A$25,A14)</f>
-        <v>22200</v>
+        <f aca="false">SUMIFS('저렴한 버전'!$J$6:$J$26,'저렴한 버전'!$A$6:$A$26,A14)</f>
+        <v>33400</v>
       </c>
       <c r="D14" s="6" t="n">
         <f aca="false">SUMIFS('일반 서보 버전'!$J$6:$J$26,'일반 서보 버전'!$A$6:$A$26,A14)</f>
@@ -8580,7 +8969,7 @@
         <v>33000</v>
       </c>
       <c r="C15" s="6" t="n">
-        <f aca="false">SUMIFS('저렴한 버전'!$J$6:$J$25,'저렴한 버전'!$A$6:$A$25,A15)</f>
+        <f aca="false">SUMIFS('저렴한 버전'!$J$6:$J$26,'저렴한 버전'!$A$6:$A$26,A15)</f>
         <v>33000</v>
       </c>
       <c r="D15" s="6" t="n">
@@ -8597,7 +8986,7 @@
         <v>55000</v>
       </c>
       <c r="C16" s="6" t="n">
-        <f aca="false">SUMIFS('저렴한 버전'!$J$6:$J$25,'저렴한 버전'!$A$6:$A$25,A16)</f>
+        <f aca="false">SUMIFS('저렴한 버전'!$J$6:$J$26,'저렴한 버전'!$A$6:$A$26,A16)</f>
         <v>0</v>
       </c>
       <c r="D16" s="6" t="n">
@@ -8614,7 +9003,7 @@
         <v>0</v>
       </c>
       <c r="C17" s="6" t="n">
-        <f aca="false">SUMIFS('저렴한 버전'!$J$6:$J$25,'저렴한 버전'!$A$6:$A$25,A17)</f>
+        <f aca="false">SUMIFS('저렴한 버전'!$J$6:$J$26,'저렴한 버전'!$A$6:$A$26,A17)</f>
         <v>0</v>
       </c>
       <c r="D17" s="6" t="n">
@@ -8628,11 +9017,11 @@
       </c>
       <c r="B18" s="8" t="n">
         <f aca="false">오리지널!$J$38</f>
-        <v>862602</v>
+        <v>896602</v>
       </c>
       <c r="C18" s="8" t="n">
-        <f aca="false">'저렴한 버전'!$J$27</f>
-        <v>549466</v>
+        <f aca="false">'저렴한 버전'!$J$28</f>
+        <v>560666</v>
       </c>
       <c r="D18" s="8" t="n">
         <f aca="false">'일반 서보 버전'!$J$28</f>
@@ -10303,14 +10692,14 @@
         <v>201</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
         <v>14</v>
       </c>
       <c r="B33" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="20" t="s">
         <v>203</v>
       </c>
       <c r="D33" s="15" t="n">
@@ -10324,34 +10713,36 @@
         <v>1</v>
       </c>
       <c r="G33" s="16" t="n">
-        <v>6000</v>
+        <v>40000</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>72</v>
       </c>
       <c r="I33" s="18" t="n">
         <f aca="false">IF(H33="USD",G33*비교!$C$4,G33)</f>
-        <v>6000</v>
+        <v>40000</v>
       </c>
       <c r="J33" s="18" t="n">
         <f aca="false">F33*I33</f>
-        <v>6000</v>
+        <v>40000</v>
       </c>
       <c r="K33" s="13" t="s">
         <v>101</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="M33" s="19" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N33" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="O33" s="20"/>
+      <c r="O33" s="14" t="s">
+        <v>206</v>
+      </c>
       <c r="P33" s="14" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10359,10 +10750,10 @@
         <v>15</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D34" s="15" t="n">
         <v>1</v>
@@ -10395,14 +10786,14 @@
         <v>113</v>
       </c>
       <c r="M34" s="19" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N34" s="13" t="s">
         <v>115</v>
       </c>
       <c r="O34" s="20"/>
       <c r="P34" s="20" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10410,10 +10801,10 @@
         <v>15</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D35" s="15" t="n">
         <v>1</v>
@@ -10446,14 +10837,14 @@
         <v>113</v>
       </c>
       <c r="M35" s="19" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N35" s="13" t="s">
         <v>115</v>
       </c>
       <c r="O35" s="20"/>
       <c r="P35" s="20" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10461,10 +10852,10 @@
         <v>16</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D36" s="15" t="n">
         <v>1</v>
@@ -10497,14 +10888,14 @@
         <v>113</v>
       </c>
       <c r="M36" s="19" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N36" s="13" t="s">
         <v>115</v>
       </c>
       <c r="O36" s="20"/>
       <c r="P36" s="20" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10513,16 +10904,16 @@
       </c>
       <c r="J38" s="8" t="n">
         <f aca="false">SUM(J6:J36)</f>
-        <v>862602</v>
+        <v>896602</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I39" s="7" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J39" s="30" t="n">
         <f aca="false">IFERROR(J6/J38,0)</f>
-        <v>0.489681220307859</v>
+        <v>0.471112043024664</v>
       </c>
     </row>
   </sheetData>
@@ -10555,7 +10946,7 @@
     <hyperlink ref="M30" r:id="rId25" display="https://www.aliexpress.com/w/wholesale-10x15x3-bearing.html?SortType=price_asc"/>
     <hyperlink ref="M31" r:id="rId26" display="https://www.aliexpress.com/w/wholesale-M2-M2.5-M3-screw-kit.html?SortType=price_asc"/>
     <hyperlink ref="M32" r:id="rId27" display="https://www.aliexpress.com/w/wholesale-M2-heat-set-insert.html?SortType=price_asc"/>
-    <hyperlink ref="M33" r:id="rId28" display="https://www.aliexpress.com/w/wholesale-carbon-fiber-plate-1mm-100x100.html?SortType=price_asc"/>
+    <hyperlink ref="M33" r:id="rId28" display="https://search.shopping.naver.com/search/all?query=%EC%95%8C%EB%A3%A8%EB%AF%B8%EB%8A%84+%EB%A0%88%EC%9D%B4%EC%A0%80+%EA%B0%80%EA%B3%B5+%EC%86%8C%EB%9F%89&amp;sort=price_asc"/>
     <hyperlink ref="M34" r:id="rId29" display="https://search.shopping.naver.com/search/all?query=PETG+%ED%95%84%EB%9D%BC%EB%A9%98%ED%8A%B8+1kg&amp;sort=price_asc"/>
     <hyperlink ref="M35" r:id="rId30" display="https://search.shopping.naver.com/search/all?query=TPU+95A+%ED%95%84%EB%9D%BC%EB%A9%98%ED%8A%B8&amp;sort=price_asc"/>
     <hyperlink ref="M36" r:id="rId31" display="https://search.shopping.naver.com/search/all?query=Xbox+%EB%AC%B4%EC%84%A0+%EC%BB%A8%ED%8A%B8%EB%A1%A4%EB%9F%AC&amp;sort=price_asc"/>
@@ -10576,7 +10967,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -10598,12 +10989,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10719,10 +11110,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D7" s="15" t="n">
         <v>1</v>
@@ -10755,14 +11146,14 @@
         <v>113</v>
       </c>
       <c r="M7" s="19" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N7" s="13" t="s">
         <v>115</v>
       </c>
       <c r="O7" s="20"/>
       <c r="P7" s="14" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10874,10 +11265,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>1</v>
@@ -10910,14 +11301,14 @@
         <v>113</v>
       </c>
       <c r="M10" s="19" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N10" s="13" t="s">
         <v>115</v>
       </c>
       <c r="O10" s="20"/>
       <c r="P10" s="14" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11593,15 +11984,15 @@
         <v>197</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="D24" s="15" t="n">
         <v>1</v>
@@ -11613,35 +12004,35 @@
         <f aca="false">D24+E24*비교!$C$5</f>
         <v>1</v>
       </c>
-      <c r="G24" s="16" t="n">
-        <v>15000</v>
+      <c r="G24" s="29" t="n">
+        <v>8</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="I24" s="18" t="n">
         <f aca="false">IF(H24="USD",G24*비교!$C$4,G24)</f>
-        <v>15000</v>
+        <v>11200</v>
       </c>
       <c r="J24" s="18" t="n">
         <f aca="false">F24*I24</f>
-        <v>15000</v>
+        <v>11200</v>
       </c>
       <c r="K24" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="L24" s="13" t="s">
-        <v>113</v>
+      <c r="L24" s="17" t="s">
+        <v>176</v>
       </c>
       <c r="M24" s="19" t="s">
-        <v>208</v>
+        <v>177</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>115</v>
+        <v>178</v>
       </c>
       <c r="O24" s="20"/>
-      <c r="P24" s="20" t="s">
-        <v>209</v>
+      <c r="P24" s="14" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11649,10 +12040,10 @@
         <v>15</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D25" s="15" t="n">
         <v>1</v>
@@ -11665,18 +12056,18 @@
         <v>1</v>
       </c>
       <c r="G25" s="16" t="n">
-        <v>18000</v>
+        <v>15000</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>72</v>
       </c>
       <c r="I25" s="18" t="n">
         <f aca="false">IF(H25="USD",G25*비교!$C$4,G25)</f>
-        <v>18000</v>
+        <v>15000</v>
       </c>
       <c r="J25" s="18" t="n">
         <f aca="false">F25*I25</f>
-        <v>18000</v>
+        <v>15000</v>
       </c>
       <c r="K25" s="13" t="s">
         <v>101</v>
@@ -11685,36 +12076,87 @@
         <v>113</v>
       </c>
       <c r="M25" s="19" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="N25" s="13" t="s">
         <v>115</v>
       </c>
       <c r="O25" s="20"/>
       <c r="P25" s="20" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="C26" s="14" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I27" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J27" s="8" t="n">
-        <f aca="false">SUM(J6:J25)</f>
-        <v>549466</v>
+      <c r="D26" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <f aca="false">D26+E26*비교!$C$5</f>
+        <v>1</v>
+      </c>
+      <c r="G26" s="16" t="n">
+        <v>18000</v>
+      </c>
+      <c r="H26" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="I26" s="18" t="n">
+        <f aca="false">IF(H26="USD",G26*비교!$C$4,G26)</f>
+        <v>18000</v>
+      </c>
+      <c r="J26" s="18" t="n">
+        <f aca="false">F26*I26</f>
+        <v>18000</v>
+      </c>
+      <c r="K26" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="L26" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="M26" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="N26" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I28" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="J28" s="30" t="n">
-        <f aca="false">IFERROR(J6/J27,0)</f>
-        <v>0.67265308499525</v>
+        <v>18</v>
+      </c>
+      <c r="J28" s="8" t="n">
+        <f aca="false">SUM(J6:J26)</f>
+        <v>560666</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I29" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="J29" s="30" t="n">
+        <f aca="false">IFERROR(J6/J28,0)</f>
+        <v>0.659216003824024</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:P25"/>
+  <autoFilter ref="A5:P26"/>
   <hyperlinks>
     <hyperlink ref="M6" r:id="rId1" display="https://www.robotis.com/shop/item.php?it_id=902-0163-000"/>
     <hyperlink ref="M7" r:id="rId2" display="https://search.shopping.naver.com/search/all?query=CP2102+USB+TTL+%EB%AA%A8%EB%93%88&amp;sort=price_asc"/>
@@ -11734,8 +12176,9 @@
     <hyperlink ref="M21" r:id="rId16" display="https://www.aliexpress.com/w/wholesale-16x22x4-bearing.html?SortType=price_asc"/>
     <hyperlink ref="M22" r:id="rId17" display="https://www.aliexpress.com/w/wholesale-10x15x3-bearing.html?SortType=price_asc"/>
     <hyperlink ref="M23" r:id="rId18" display="https://www.aliexpress.com/w/wholesale-M2-M2.5-M3-screw-kit.html?SortType=price_asc"/>
-    <hyperlink ref="M24" r:id="rId19" display="https://search.shopping.naver.com/search/all?query=PETG+%ED%95%84%EB%9D%BC%EB%A9%98%ED%8A%B8+1kg&amp;sort=price_asc"/>
-    <hyperlink ref="M25" r:id="rId20" display="https://search.shopping.naver.com/search/all?query=TPU+95A+%ED%95%84%EB%9D%BC%EB%A9%98%ED%8A%B8&amp;sort=price_asc"/>
+    <hyperlink ref="M24" r:id="rId19" display="https://jlcpcb.com/"/>
+    <hyperlink ref="M25" r:id="rId20" display="https://search.shopping.naver.com/search/all?query=PETG+%ED%95%84%EB%9D%BC%EB%A9%98%ED%8A%B8+1kg&amp;sort=price_asc"/>
+    <hyperlink ref="M26" r:id="rId21" display="https://search.shopping.naver.com/search/all?query=TPU+95A+%ED%95%84%EB%9D%BC%EB%A9%98%ED%8A%B8&amp;sort=price_asc"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -11744,7 +12187,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId21"/>
+  <drawing r:id="rId22"/>
 </worksheet>
 </file>
 
@@ -11775,12 +12218,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="31" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11843,10 +12286,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="D6" s="15" t="n">
         <v>11</v>
@@ -11876,19 +12319,19 @@
         <v>101</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="M6" s="19" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="N6" s="13" t="s">
         <v>76</v>
       </c>
       <c r="O6" s="20" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="P6" s="20" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11896,10 +12339,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D7" s="15" t="n">
         <v>4</v>
@@ -11932,16 +12375,16 @@
         <v>113</v>
       </c>
       <c r="M7" s="19" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="N7" s="13" t="s">
         <v>115</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="P7" s="14" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11949,10 +12392,10 @@
         <v>8</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D8" s="15" t="n">
         <v>11</v>
@@ -11985,14 +12428,14 @@
         <v>102</v>
       </c>
       <c r="M8" s="19" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="N8" s="13" t="s">
         <v>115</v>
       </c>
       <c r="O8" s="20"/>
       <c r="P8" s="20" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12000,10 +12443,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D9" s="15" t="n">
         <v>15</v>
@@ -12036,14 +12479,14 @@
         <v>102</v>
       </c>
       <c r="M9" s="19" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="N9" s="13" t="s">
         <v>115</v>
       </c>
       <c r="O9" s="20"/>
       <c r="P9" s="20" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12051,10 +12494,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="D10" s="23" t="n">
         <v>1</v>
@@ -12084,19 +12527,19 @@
         <v>73</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="M10" s="27" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="N10" s="21" t="s">
         <v>76</v>
       </c>
       <c r="O10" s="28" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="P10" s="22" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12104,10 +12547,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>1</v>
@@ -12140,7 +12583,7 @@
         <v>113</v>
       </c>
       <c r="M11" s="19" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N11" s="13" t="s">
         <v>115</v>
@@ -12153,10 +12596,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>1</v>
@@ -12189,16 +12632,16 @@
         <v>102</v>
       </c>
       <c r="M12" s="19" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="N12" s="13" t="s">
         <v>115</v>
       </c>
       <c r="O12" s="14" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="P12" s="20" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12206,10 +12649,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>4</v>
@@ -12242,16 +12685,16 @@
         <v>113</v>
       </c>
       <c r="M13" s="19" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="N13" s="13" t="s">
         <v>115</v>
       </c>
       <c r="O13" s="20" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="P13" s="14" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12259,10 +12702,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>1</v>
@@ -12295,14 +12738,14 @@
         <v>113</v>
       </c>
       <c r="M14" s="19" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="N14" s="13" t="s">
         <v>115</v>
       </c>
       <c r="O14" s="20"/>
       <c r="P14" s="20" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12310,10 +12753,10 @@
         <v>17</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>1</v>
@@ -12346,16 +12789,16 @@
         <v>113</v>
       </c>
       <c r="M15" s="19" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="N15" s="13" t="s">
         <v>115</v>
       </c>
       <c r="O15" s="20" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="P15" s="14" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12363,10 +12806,10 @@
         <v>17</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="D16" s="15" t="n">
         <v>1</v>
@@ -12399,14 +12842,14 @@
         <v>113</v>
       </c>
       <c r="M16" s="19" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="N16" s="13" t="s">
         <v>115</v>
       </c>
       <c r="O16" s="20"/>
       <c r="P16" s="20" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12414,10 +12857,10 @@
         <v>12</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>1</v>
@@ -12450,14 +12893,14 @@
         <v>113</v>
       </c>
       <c r="M17" s="19" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="N17" s="13" t="s">
         <v>115</v>
       </c>
       <c r="O17" s="20"/>
       <c r="P17" s="20" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12465,10 +12908,10 @@
         <v>12</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>1</v>
@@ -12501,14 +12944,14 @@
         <v>113</v>
       </c>
       <c r="M18" s="19" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="N18" s="13" t="s">
         <v>115</v>
       </c>
       <c r="O18" s="20"/>
       <c r="P18" s="20" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12516,10 +12959,10 @@
         <v>12</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>1</v>
@@ -12552,14 +12995,14 @@
         <v>113</v>
       </c>
       <c r="M19" s="19" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="N19" s="13" t="s">
         <v>115</v>
       </c>
       <c r="O19" s="20"/>
       <c r="P19" s="14" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12567,10 +13010,10 @@
         <v>12</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="D20" s="15" t="n">
         <v>2</v>
@@ -12610,7 +13053,7 @@
       </c>
       <c r="O20" s="20"/>
       <c r="P20" s="14" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12618,10 +13061,10 @@
         <v>12</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D21" s="15" t="n">
         <v>2</v>
@@ -12654,14 +13097,14 @@
         <v>113</v>
       </c>
       <c r="M21" s="19" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="N21" s="13" t="s">
         <v>115</v>
       </c>
       <c r="O21" s="20"/>
       <c r="P21" s="20" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12669,10 +13112,10 @@
         <v>12</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="D22" s="15" t="n">
         <v>1</v>
@@ -12705,7 +13148,7 @@
         <v>113</v>
       </c>
       <c r="M22" s="19" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>115</v>
@@ -12718,10 +13161,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="D23" s="15" t="n">
         <v>16</v>
@@ -12754,16 +13197,16 @@
         <v>102</v>
       </c>
       <c r="M23" s="19" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>115</v>
       </c>
       <c r="O23" s="20" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="P23" s="20" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12774,7 +13217,7 @@
         <v>194</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="D24" s="15" t="n">
         <v>1</v>
@@ -12807,14 +13250,14 @@
         <v>102</v>
       </c>
       <c r="M24" s="19" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>115</v>
       </c>
       <c r="O24" s="20"/>
       <c r="P24" s="20" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12822,10 +13265,10 @@
         <v>15</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D25" s="15" t="n">
         <v>1</v>
@@ -12858,14 +13301,14 @@
         <v>113</v>
       </c>
       <c r="M25" s="19" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N25" s="13" t="s">
         <v>115</v>
       </c>
       <c r="O25" s="20"/>
       <c r="P25" s="14" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12873,10 +13316,10 @@
         <v>15</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="D26" s="15" t="n">
         <v>1</v>
@@ -12909,14 +13352,14 @@
         <v>113</v>
       </c>
       <c r="M26" s="19" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>115</v>
       </c>
       <c r="O26" s="20"/>
       <c r="P26" s="20" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12930,7 +13373,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I29" s="7" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J29" s="30" t="n">
         <f aca="false">IFERROR(J6/J28,0)</f>
@@ -12993,7 +13436,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="33" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>4</v>
@@ -13002,33 +13445,33 @@
         <v>57</v>
       </c>
       <c r="D1" s="33" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="E1" s="33" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="F1" s="33" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>69</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="34" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C2" s="34" t="n">
         <v>1</v>
@@ -13046,21 +13489,21 @@
         <v>6.69</v>
       </c>
       <c r="H2" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I2" s="35" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="J2" s="34" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="34" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C3" s="34" t="n">
         <v>1</v>
@@ -13078,19 +13521,19 @@
         <v>7.88</v>
       </c>
       <c r="H3" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I3" s="34"/>
       <c r="J3" s="34" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="34" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C4" s="34" t="n">
         <v>1</v>
@@ -13108,21 +13551,21 @@
         <v>6.69</v>
       </c>
       <c r="H4" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I4" s="35" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="J4" s="34" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="34" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C5" s="34" t="n">
         <v>1</v>
@@ -13140,19 +13583,19 @@
         <v>7.88</v>
       </c>
       <c r="H5" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I5" s="34"/>
       <c r="J5" s="34" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="34" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C6" s="34" t="n">
         <v>1</v>
@@ -13170,19 +13613,19 @@
         <v>0.46</v>
       </c>
       <c r="H6" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I6" s="34"/>
       <c r="J6" s="34" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="34" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C7" s="34" t="n">
         <v>2</v>
@@ -13199,22 +13642,22 @@
       <c r="G7" s="34" t="n">
         <v>0.63</v>
       </c>
-      <c r="H7" s="34" t="s">
-        <v>334</v>
+      <c r="H7" s="35" t="s">
+        <v>339</v>
       </c>
       <c r="I7" s="35" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="J7" s="34" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="34" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C8" s="34" t="n">
         <v>1</v>
@@ -13232,19 +13675,19 @@
         <v>23.8</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I8" s="34"/>
       <c r="J8" s="34" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="34" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C9" s="34" t="n">
         <v>1</v>
@@ -13262,21 +13705,21 @@
         <v>1.57</v>
       </c>
       <c r="H9" s="34" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="I9" s="35" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="J9" s="34" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="34" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C10" s="34" t="n">
         <v>1</v>
@@ -13294,19 +13737,19 @@
         <v>5.82</v>
       </c>
       <c r="H10" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I10" s="34"/>
       <c r="J10" s="34" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="34" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C11" s="34" t="n">
         <v>1</v>
@@ -13324,19 +13767,19 @@
         <v>12.18</v>
       </c>
       <c r="H11" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I11" s="34"/>
       <c r="J11" s="34" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="34" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C12" s="34" t="n">
         <v>1</v>
@@ -13354,19 +13797,19 @@
         <v>12.18</v>
       </c>
       <c r="H12" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I12" s="34"/>
       <c r="J12" s="34" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B13" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C13" s="34" t="n">
         <v>2</v>
@@ -13384,19 +13827,19 @@
         <v>4.52</v>
       </c>
       <c r="H13" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I13" s="34"/>
       <c r="J13" s="34" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="34" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B14" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C14" s="34" t="n">
         <v>1</v>
@@ -13414,19 +13857,19 @@
         <v>9.36</v>
       </c>
       <c r="H14" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I14" s="34"/>
       <c r="J14" s="34" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="34" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B15" s="35" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C15" s="34" t="n">
         <v>1</v>
@@ -13444,21 +13887,21 @@
         <v>18.6</v>
       </c>
       <c r="H15" s="34" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="I15" s="35" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="J15" s="34" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="34" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C16" s="34" t="n">
         <v>1</v>
@@ -13476,19 +13919,19 @@
         <v>11.39</v>
       </c>
       <c r="H16" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I16" s="34"/>
       <c r="J16" s="34" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="34" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C17" s="34" t="n">
         <v>2</v>
@@ -13506,19 +13949,19 @@
         <v>3.41</v>
       </c>
       <c r="H17" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I17" s="34"/>
       <c r="J17" s="34" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="34" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C18" s="34" t="n">
         <v>1</v>
@@ -13536,21 +13979,21 @@
         <v>2.8</v>
       </c>
       <c r="H18" s="34" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="I18" s="34" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="J18" s="34" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="34" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B19" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C19" s="34" t="n">
         <v>1</v>
@@ -13568,19 +14011,19 @@
         <v>1.1</v>
       </c>
       <c r="H19" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I19" s="34"/>
       <c r="J19" s="34" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="34" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B20" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C20" s="34" t="n">
         <v>1</v>
@@ -13598,19 +14041,19 @@
         <v>7.52</v>
       </c>
       <c r="H20" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I20" s="34"/>
       <c r="J20" s="34" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="34" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="B21" s="35" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C21" s="34" t="n">
         <v>2</v>
@@ -13627,20 +14070,22 @@
       <c r="G21" s="34" t="n">
         <v>0.4</v>
       </c>
-      <c r="H21" s="34" t="s">
-        <v>373</v>
-      </c>
-      <c r="I21" s="34"/>
+      <c r="H21" s="35" t="s">
+        <v>378</v>
+      </c>
+      <c r="I21" s="35" t="s">
+        <v>379</v>
+      </c>
       <c r="J21" s="34" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="34" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B22" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C22" s="34" t="n">
         <v>1</v>
@@ -13658,19 +14103,19 @@
         <v>4.11</v>
       </c>
       <c r="H22" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I22" s="34"/>
       <c r="J22" s="34" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="34" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B23" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C23" s="34" t="n">
         <v>1</v>
@@ -13688,19 +14133,19 @@
         <v>4.25</v>
       </c>
       <c r="H23" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I23" s="34"/>
       <c r="J23" s="34" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="34" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B24" s="35" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C24" s="34" t="n">
         <v>1</v>
@@ -13718,21 +14163,21 @@
         <v>51.56</v>
       </c>
       <c r="H24" s="34" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="I24" s="35" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="J24" s="34" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="34" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B25" s="35" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C25" s="34" t="n">
         <v>1</v>
@@ -13750,21 +14195,21 @@
         <v>3.02</v>
       </c>
       <c r="H25" s="34" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="I25" s="35" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="J25" s="34" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="34" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B26" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C26" s="34" t="n">
         <v>1</v>
@@ -13782,19 +14227,19 @@
         <v>10.49</v>
       </c>
       <c r="H26" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I26" s="34"/>
       <c r="J26" s="34" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="34" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B27" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C27" s="34" t="n">
         <v>1</v>
@@ -13812,19 +14257,19 @@
         <v>11.22</v>
       </c>
       <c r="H27" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I27" s="34"/>
       <c r="J27" s="34" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="34" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B28" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C28" s="34" t="n">
         <v>4</v>
@@ -13842,21 +14287,21 @@
         <v>1.03</v>
       </c>
       <c r="H28" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I28" s="35" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="J28" s="34" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="34" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B29" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C29" s="34" t="n">
         <v>2</v>
@@ -13874,21 +14319,21 @@
         <v>11.81</v>
       </c>
       <c r="H29" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I29" s="35" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="J29" s="34" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="34" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B30" s="35" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C30" s="34" t="n">
         <v>11</v>
@@ -13906,21 +14351,21 @@
         <v>0.49</v>
       </c>
       <c r="H30" s="35" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="I30" s="35" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="J30" s="34" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="34" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B31" s="35" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C31" s="34" t="n">
         <v>3</v>
@@ -13938,21 +14383,21 @@
         <v>0.19</v>
       </c>
       <c r="H31" s="35" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="I31" s="35" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="J31" s="34" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="34" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B32" s="35" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C32" s="34" t="n">
         <v>1</v>
@@ -13970,21 +14415,21 @@
         <v>2.7</v>
       </c>
       <c r="H32" s="34" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="I32" s="35" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="J32" s="34" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="34" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="B33" s="35" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C33" s="34" t="n">
         <v>1</v>
@@ -14002,21 +14447,21 @@
         <v>6.25</v>
       </c>
       <c r="H33" s="34" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="I33" s="35" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="J33" s="34" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="34" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="B34" s="35" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C34" s="34" t="n">
         <v>1</v>
@@ -14034,21 +14479,21 @@
         <v>6.25</v>
       </c>
       <c r="H34" s="34" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="I34" s="35" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="J34" s="34" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="34" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="B35" s="35" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C35" s="34" t="n">
         <v>1</v>
@@ -14066,19 +14511,19 @@
         <v>6.13</v>
       </c>
       <c r="H35" s="34" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="I35" s="34"/>
       <c r="J35" s="34" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="34" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="B36" s="35" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C36" s="34" t="n">
         <v>4</v>
@@ -14096,21 +14541,21 @@
         <v>2.81</v>
       </c>
       <c r="H36" s="34" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="I36" s="35" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="J36" s="34" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="34" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="B37" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C37" s="34" t="n">
         <v>1</v>
@@ -14128,19 +14573,19 @@
         <v>29.87</v>
       </c>
       <c r="H37" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I37" s="34"/>
       <c r="J37" s="34" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="34" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="B38" s="35" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C38" s="34" t="n">
         <v>1</v>
@@ -14157,22 +14602,22 @@
       <c r="G38" s="34" t="n">
         <v>1.42</v>
       </c>
-      <c r="H38" s="34" t="s">
-        <v>334</v>
+      <c r="H38" s="35" t="s">
+        <v>339</v>
       </c>
       <c r="I38" s="35" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="J38" s="34" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="34" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="B39" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C39" s="34" t="n">
         <v>1</v>
@@ -14190,19 +14635,19 @@
         <v>4.15</v>
       </c>
       <c r="H39" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I39" s="34"/>
       <c r="J39" s="34" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="34" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B40" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C40" s="34" t="n">
         <v>1</v>
@@ -14220,19 +14665,19 @@
         <v>4.15</v>
       </c>
       <c r="H40" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I40" s="34"/>
       <c r="J40" s="34" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="34" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="B41" s="35" t="s">
-        <v>426</v>
+        <v>338</v>
       </c>
       <c r="C41" s="34" t="n">
         <v>2</v>
@@ -14249,22 +14694,22 @@
       <c r="G41" s="34" t="n">
         <v>0.75</v>
       </c>
-      <c r="H41" s="34" t="s">
-        <v>427</v>
+      <c r="H41" s="35" t="s">
+        <v>339</v>
       </c>
       <c r="I41" s="35" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="J41" s="34" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="34" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B42" s="35" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C42" s="34" t="n">
         <v>15</v>
@@ -14285,18 +14730,18 @@
         <v>71</v>
       </c>
       <c r="I42" s="35" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="J42" s="34" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="34" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B43" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C43" s="34" t="n">
         <v>2</v>
@@ -14314,19 +14759,19 @@
         <v>2.82</v>
       </c>
       <c r="H43" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I43" s="34"/>
       <c r="J43" s="34" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="34" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B44" s="35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C44" s="34" t="n">
         <v>1</v>
@@ -14344,16 +14789,16 @@
         <v>4.56</v>
       </c>
       <c r="H44" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I44" s="34"/>
       <c r="J44" s="34" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
